--- a/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T22:41:23+00:00</t>
+    <t>2026-09-15T14:01:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:01:05+00:00</t>
+    <t>2026-09-15T17:45:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T17:45:52+00:00</t>
+    <t>2026-09-15T20:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T20:38:45+00:00</t>
+    <t>2026-09-16T05:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T05:15:10+00:00</t>
+    <t>2026-09-16T08:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:10:08+00:00</t>
+    <t>2026-09-17T08:26:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T08:26:08+00:00</t>
+    <t>2026-09-17T12:53:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-icu-muv-koerperlaenge.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3654" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3655" uniqueCount="560">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:53:08+00:00</t>
+    <t>2026-09-23T08:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,7 +422,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
@@ -460,7 +460,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -484,7 +484,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -528,7 +528,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -628,7 +628,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -707,7 +707,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -916,7 +916,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -1088,7 +1088,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1108,7 +1108,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t xml:space="preserve">Reference(Encounter)
 </t>
   </si>
   <si>
@@ -1244,7 +1244,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1422,7 +1422,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1451,7 +1451,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>Observation.note</t>
@@ -1486,6 +1486,9 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
+    <t>Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
     <t>https://gematik.de/fhir/isik/ValueSet/vs-mii-icu-bodysite-observation-monitoring-und-vitaldaten</t>
   </si>
   <si>
@@ -1504,13 +1507,13 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
   </si>
   <si>
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(Specimen)
 </t>
   </si>
   <si>
@@ -1526,7 +1529,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
+    <t xml:space="preserve">Reference(Device|DeviceMetric)
 </t>
   </si>
   <si>
@@ -1588,7 +1591,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1629,7 +1632,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
   </si>
   <si>
     <t>Observation.referenceRange.appliesTo</t>
@@ -1650,7 +1653,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1681,7 +1684,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
 </t>
   </si>
   <si>
@@ -1697,7 +1700,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
 </t>
   </si>
   <si>
@@ -2105,7 +2108,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.13671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="94.96484375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -6043,7 +6046,7 @@
         <v>74</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>75</v>
@@ -11127,9 +11130,11 @@
       <c r="X88" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="Y88" s="2"/>
+      <c r="Y88" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="Z88" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>75</v>
@@ -11164,10 +11169,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11193,16 +11198,16 @@
         <v>213</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>392</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>75</v>
@@ -11230,10 +11235,10 @@
         <v>147</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>75</v>
@@ -11251,7 +11256,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>73</v>
@@ -11268,10 +11273,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11294,16 +11299,16 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11353,7 +11358,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>73</v>
@@ -11370,10 +11375,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11396,16 +11401,16 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -11455,7 +11460,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>73</v>
@@ -11472,10 +11477,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11498,19 +11503,19 @@
         <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>75</v>
@@ -11559,7 +11564,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>73</v>
@@ -11571,15 +11576,15 @@
         <v>75</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11676,10 +11681,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11778,14 +11783,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -11807,10 +11812,10 @@
         <v>102</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>105</v>
@@ -11865,7 +11870,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>73</v>
@@ -11882,10 +11887,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11908,13 +11913,13 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -11965,7 +11970,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>73</v>
@@ -11974,7 +11979,7 @@
         <v>82</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>94</v>
@@ -11982,10 +11987,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12008,13 +12013,13 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -12065,16 +12070,16 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI97" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>94</v>
@@ -12082,10 +12087,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12111,16 +12116,16 @@
         <v>213</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>75</v>
@@ -12148,10 +12153,10 @@
         <v>161</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>75</v>
@@ -12169,7 +12174,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>73</v>
@@ -12186,10 +12191,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12215,16 +12220,16 @@
         <v>213</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>75</v>
@@ -12252,10 +12257,10 @@
         <v>147</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>75</v>
@@ -12273,7 +12278,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>73</v>
@@ -12290,10 +12295,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12316,17 +12321,17 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>75</v>
@@ -12375,7 +12380,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>73</v>
@@ -12392,10 +12397,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12421,10 +12426,10 @@
         <v>96</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -12475,7 +12480,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>73</v>
@@ -12492,10 +12497,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12518,16 +12523,16 @@
         <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -12577,7 +12582,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>73</v>
@@ -12594,10 +12599,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12620,16 +12625,16 @@
         <v>83</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -12679,7 +12684,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>73</v>
@@ -12696,10 +12701,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12722,19 +12727,19 @@
         <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>75</v>
@@ -12783,7 +12788,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>73</v>
@@ -12800,10 +12805,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12900,10 +12905,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13002,14 +13007,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13031,10 +13036,10 @@
         <v>102</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>105</v>
@@ -13089,7 +13094,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>73</v>
@@ -13106,10 +13111,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13135,13 +13140,13 @@
         <v>213</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O108" t="s" s="2">
         <v>284</v>
@@ -13193,7 +13198,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -13210,10 +13215,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13239,13 +13244,13 @@
         <v>395</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M109" t="s" s="2">
         <v>397</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O109" t="s" s="2">
         <v>399</v>
@@ -13297,7 +13302,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>73</v>
@@ -13314,10 +13319,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13343,13 +13348,13 @@
         <v>213</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O110" t="s" s="2">
         <v>443</v>
@@ -13401,7 +13406,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>73</v>
@@ -13418,10 +13423,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13505,7 +13510,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>73</v>
@@ -13522,10 +13527,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13551,16 +13556,16 @@
         <v>76</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>75</v>
@@ -13609,7 +13614,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>73</v>
